--- a/02_测试学习/03_练习题/测试练习.xlsx
+++ b/02_测试学习/03_练习题/测试练习.xlsx
@@ -7,7 +7,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9F7B11-CA12-4D82-8F02-0C78F3496E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81747FAC-DEF3-41EF-9A33-891219698A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
   </bookViews>
@@ -236,8 +236,11 @@
         <color rgb="FF000000"/>
         <family val="2"/>
       </rPr>
-      <t>显示无效银行卡
-吐出卡，返回开始界面</t>
+      <t xml:space="preserve">显示无效银行卡
+</t>
+    </r>
+    <r>
+      <t>吐出卡，返回开始界面</t>
     </r>
   </si>
   <si>
@@ -292,8 +295,11 @@
         <color rgb="FF000000"/>
         <family val="2"/>
       </rPr>
-      <t>提示密码错误
-请求重新输入</t>
+      <t xml:space="preserve">提示密码错误
+</t>
+    </r>
+    <r>
+      <t>请求重新输入</t>
     </r>
   </si>
   <si>
@@ -313,8 +319,11 @@
         <color rgb="FF000000"/>
         <family val="2"/>
       </rPr>
-      <t>提示第二次密码错误
-请求重新输入</t>
+      <t xml:space="preserve">提示第二次密码错误
+</t>
+    </r>
+    <r>
+      <t>请求重新输入</t>
     </r>
   </si>
   <si>
@@ -373,8 +382,11 @@
         <color rgb="FF000000"/>
         <family val="2"/>
       </rPr>
-      <t>提示卡余额不足
-请重新输入</t>
+      <t xml:space="preserve">提示卡余额不足
+</t>
+    </r>
+    <r>
+      <t>请重新输入</t>
     </r>
   </si>
   <si>
@@ -426,8 +438,11 @@
         <color rgb="FF000000"/>
         <family val="2"/>
       </rPr>
-      <t>提示卡超出限额
-请重新输入</t>
+      <t xml:space="preserve">提示卡超出限额
+</t>
+    </r>
+    <r>
+      <t>请重新输入</t>
     </r>
   </si>
   <si>
@@ -555,14 +570,14 @@
     </font>
     <font>
       <name val="等线"/>
-      <sz val="11.00"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9.00"/>
+      <color rgb="FF000000"/>
       <family val="2"/>
     </font>
     <font>
       <name val="等线"/>
-      <sz val="9.00"/>
-      <color rgb="FF000000"/>
+      <sz val="11.00"/>
+      <color rgb="FFFF0000"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -575,19 +590,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9DC3E6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,6 +603,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DC3E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -696,67 +711,67 @@
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="2" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="2" applyFont="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" applyFont="1" borderId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" applyFont="1" borderId="4" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf fontId="3" applyFont="1" fillId="6" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="1" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf fontId="2" applyFont="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" applyFont="1" borderId="5" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" applyAlignment="1">
+    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
+    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="10" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
+    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="7" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" borderId="4" applyBorder="1" applyAlignment="1">
+    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="4" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="6" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" borderId="3" applyBorder="1" applyAlignment="1">
+    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="2" applyBorder="1" applyAlignment="1">
+    <xf xfId="10" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" borderId="5" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="6" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
+    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="7" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="6" applyFill="1" borderId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
